--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,87 +713,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Developer (Unity Catalog Migration)</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DysrupIT</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
+          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Databricks Developer (Unity Catalog Migration)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DysrupIT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Onshore - Sr Engg_CurationSup</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Hadoop, HDFS, Hive, HBase, YARN, Spark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7f1eb8e2a6e504b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Senior Data Ops Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Developer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Kafka Connect, PostgreSQL, ETL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98975d1b0220f278</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -2013,20 +2013,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,73 +2092,73 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer, Forward Deployed Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, ETL, ELT, dbt, CI/CD, Docker</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e265a7ba14741f6</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b9675535a55f10</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BrightVine Solutions</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Oracle Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Software Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BrightVine Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Analytics Platform Engineer Alteryx</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Garland, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT Data</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,29 +2586,29 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Data Lake Storage, Spark, Data Modeling, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3952890269a6ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Java/React FSE</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7523ee959e30aea8</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Java/React FSE</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddfa043b9e204f89</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Greenfield Associate Full Stack Developer</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate Developer, IT Applications</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Hadoop, Spark, MongoDB, Jenkins, GitHub Actions, Maven, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f79cbad8ac813d</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Automation Framework Engineer</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c357e7ee9bbbd601</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,59 +4766,59 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Database Developer Expert</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92128339a573b187</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>OpenShift Administrator</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate, PXT Analytics</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f479479b7e0ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Data Scientist Senior Associate, PXT Analytics</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f479479b7e0ed2b</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,15 +5421,470 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II - Encore Program</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>UX Software Engineer 6.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>GRVTY</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Ai Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>.NET Engineer with Dicom</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Digital Dhara LLC</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Sr. Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=387fc6b51ae76f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I - Global Servicing Technology</t>
+          <t>DEV OPS ENGINEER IV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Envision Healthcare</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
+          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Dataflow, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82541ee7f79e647f</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oracle Cloud Infrastructure Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baafd5f75dd4402a</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BrightVine Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24293ea9e15ad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Platform Engineer Alteryx</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Garland, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MongoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9998dda2a0296a</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,67 +4661,67 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
@@ -4743,20 +4743,20 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior AWS Platform Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>New Era Technology</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OpenShift Administrator</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad761b4ec5135c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate, PXT Analytics</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f479479b7e0ed2b</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Data Scientist Senior Associate, PXT Analytics</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f479479b7e0ed2b</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,225 +5666,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>UX Software Engineer 6.2026</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Johnson Controls</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>.NET Engineer with Dicom</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Digital Dhara LLC</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Onshore - Sr Engg_CurationSup</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
@@ -1978,20 +1978,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,94 +2946,94 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,19 +4451,19 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,67 +4486,67 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10d3c2eb2b954cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14312f1b5ae1eee7</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>New Era Technology</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, IAM, RDS, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34542792a9682496</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,34 +5316,34 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,322 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Data Scientist Senior Associate, PXT Analytics</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Databricks, Scala, Snowflake, dbt, Tableau, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1f479479b7e0ed2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Travel + Leisure Co.</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>UX Software Engineer 6.2026</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Johnson Controls</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>.NET Engineer with Dicom</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Digital Dhara LLC</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,77 +836,77 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac712b4e1b735d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Developer (Unity Catalog Migration)</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DysrupIT</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b253191bad860e34</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Bloomerang</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Application Development and Implementation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>ritepros</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,42 +1886,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,42 +1931,42 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Streaming Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Senior Associate - Analytics Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,67 +4416,67 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,77 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Johnson Controls</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G139"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Application Development and Implementation Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ritepros</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Spark, PySpark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd02376babaa3dee</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Business Systems Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Infoville, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Quality Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,42 +1266,42 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1868,52 +1868,52 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>pointer infotech L.L.C</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Streaming Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Spark Streaming, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6de0bab061bc9cb</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Associate - Analytics Engineer</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4413578cebf7d25</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,59 +2771,59 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,67 +4346,67 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Ai Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>.NET Engineer with Dicom</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Digital Dhara LLC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,17 +4931,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,14 +5011,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,14 +5046,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5185,111 +5185,6 @@
         </is>
       </c>
       <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Data and Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Jr Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>NAVA TECH LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
@@ -2708,17 +2708,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,59 +4276,59 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
@@ -4528,17 +4528,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Business Systems Analyst</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Infoville, Inc</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d7fde96960560b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Quality Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Data Factory, Blob Storage, Event Hubs, Scala, Splunk</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d99840edec18518b</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Streaming Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pointer infotech L.L.C</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0669283adb0994ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Sr Salesforce HealthCloud Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>TriWest Healthcare Alliance</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
@@ -4633,17 +4633,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ai Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, ETL, MLOps, CI/CD, Docker, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245ecaddb1985ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, SQL Server, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8ad5ccbc04e6be</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>.NET Engineer with Dicom</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Digital Dhara LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416c7d1cd0685efb</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,24 +4826,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,14 +4906,14 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,14 +4941,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5010,181 +5010,6 @@
         </is>
       </c>
       <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Meso Scale Diagnostics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, Databricks, BigQuery</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,129 +601,129 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=040188cbf02542cc</t>
+          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I - Global Servicing Technology</t>
+          <t>DEV OPS ENGINEER IV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Envision Healthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
+          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEV OPS ENGINEER IV</t>
+          <t>Java Platform Architect / Spring Integration Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Envision Healthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
+          <t>https://www.indeed.com/viewjob?jk=2e659cdd95ef50fa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java Platform Architect / Spring Integration Architect</t>
+          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e659cdd95ef50fa</t>
+          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
+          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Onshore - Sr Engg_CurationSup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bloomerang</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0fe96b9bdbba45</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Data Ops Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data and Cloud Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, HDFS, Hive, Sqoop, Zookeeper, YARN</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e13cb45435ccdd</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jr Data Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAVA TECH LLC</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da4ecc01920f955</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Streaming Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Spark, Scala, Kafka, NoSQL, Splunk</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7b564fddd4b752</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8ca9e790778786</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
@@ -2428,25 +2428,25 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ab7ebc9d293399</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Salesforce HealthCloud Data Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TriWest Healthcare Alliance</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4ae0d314a98a06b</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,59 +4171,59 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nitor Infotech</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, API Gateway, RDS, Azure, Blob Storage, Google Cloud Platform, GCP</t>
+          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9691a4b3c751e344</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hilti Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8b281e1b138c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>DEV OPS ENGINEER IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Envision Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I - Global Servicing Technology</t>
+          <t>Java Platform Architect / Spring Integration Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
+          <t>https://www.indeed.com/viewjob?jk=2e659cdd95ef50fa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEV OPS ENGINEER IV</t>
+          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Envision Healthcare</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
+          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Java Platform Architect / Spring Integration Architect</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e659cdd95ef50fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
+          <t>Site Reliability Engineer ll</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
+          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Onshore - Sr Engg_CurationSup</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
+          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Onshore - Sr Engg_CurationSup</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Senior Data Ops Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Engineer, Technology II (Data Engineering &amp; Architecture)</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85923548cee90695</t>
+          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,17 +3951,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer (Payments and POS Integrations)</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,59 +4136,59 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71273f666eda5a97</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Vantage Bank Texas</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=670377e753372f6a</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
@@ -4563,17 +4563,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4801,14 +4801,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4940,76 +4940,6 @@
         </is>
       </c>
       <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer ll</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72289279cfc2dcd3</t>
+          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Onshore - Sr Engg_CurationSup</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Onshore - Sr Engg_CurationSup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Ops Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,42 +1091,42 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9e63e01e919be7</t>
+          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Sr. Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Keck Medicine of USC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Preferred Credit, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Cloud, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DATA AND ANALYTICS ARCHITECT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>City of Worcester</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e51b418f356104</t>
+          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e47ba33b8611514</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,164 +2421,164 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,67 +3996,67 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vantage Bank Texas</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, ETL, ELT, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5a20dc79ac25721</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
@@ -4388,17 +4388,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,24 +4581,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,14 +4661,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,192 +4756,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DATA AND ANALYTICS ARCHITECT</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>City of Worcester</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31049f7721c1b664</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14758f985fc54f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
@@ -3968,52 +3968,52 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Founding Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Patient Funding Alternatives</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
@@ -4732,41 +4732,6 @@
       <c r="G123" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Software Engineer I - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Oozie, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,129 +496,129 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed5e67a7bd26cdb</t>
+          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer I - Global Servicing Technology</t>
+          <t>DEV OPS ENGINEER IV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Envision Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f892fe903a7c319</t>
+          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEV OPS ENGINEER IV</t>
+          <t>Java Platform Architect / Spring Integration Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Envision Healthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Spark, Scala, Snowflake, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234470a5d086eaec</t>
+          <t>https://www.indeed.com/viewjob?jk=2e659cdd95ef50fa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Platform Architect / Spring Integration Architect</t>
+          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Symhas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e659cdd95ef50fa</t>
+          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Data Engineer – Data Warehouse Migration (Contract)</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Symhas</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Snowflake, Oracle</t>
+          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db29dad2b864cc94</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Sr. Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hermosa Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, Scala, Snowflake, SQL Server, PostgreSQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4b06e145d564d5</t>
+          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hermosa Beach, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, RDS, Azure, Databricks, Medallion Architecture, GCP</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b35736fa253152e</t>
+          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II - Global Servicing Technology</t>
+          <t>Onshore - Sr Engg_CurationSup</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
+          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Global Servicing Technology</t>
+          <t>Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
+          <t>https://www.indeed.com/viewjob?jk=07502c293eb31de6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0031fd954f123a0a</t>
+          <t>https://www.indeed.com/viewjob?jk=55a217df198f7ff1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Onshore - Sr Engg_CurationSup</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3043110bea025f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Ops Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fe3c3c98332bc48</t>
+          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Cadent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Medallion Architecture, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092a3008f1f3de0c</t>
+          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Forward Deployment Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cadent</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=351e23716b572507</t>
+          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer 2, Merchandise Planning - (Hybrid, Seattle)</t>
+          <t>Sr Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Quizlet</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=976583714f7e7238</t>
+          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Data Engineer - Lilly Medicine Foundry</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Solutions Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Databricks Lakehouse</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0a76a95748095f</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Keck Medicine of USC</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2509a4fb0efe928</t>
+          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Preferred Credit, Inc.</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saint Cloud, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Medallion Architecture, Spark, PySpark, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5191b8d6d8df363b</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Senior Software Engineer, Identity Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Prove</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,19 +3751,19 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,67 +3821,67 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
@@ -3903,20 +3903,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Founding Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Patient Funding Alternatives</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, Power BI, Airflow, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4e6660d1abd6eeb</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,24 +4371,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4555,181 +4555,6 @@
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,60 +958,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7cb3f6930d19e7</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Quizlet</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a846c2cc34851159</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
@@ -1523,20 +1523,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Lilly Medicine Foundry</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, RDS, Azure, Medallion Architecture, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49198e624e4c8e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=866e6df739eb8ef0</t>
+          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Power BI, Tableau, MLOps, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6891f17a3e96ad61</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Identity Platform</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Prove</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10fd66ef196fc72</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Hadoop, Hive, Spark, Scala, Data Modeling, ETL, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd979a0715c09dce</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Greenfield Full Stack Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,29 +3566,29 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>MMOTA Automation &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer III- Eng</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,24 +4196,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bd024ab0dc6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,14 +4241,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4275,286 +4275,6 @@
         </is>
       </c>
       <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,52 +923,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, API Gateway, IAM, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33f87f7b4775762</t>
+          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>El Car Wash</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Doral, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80caa3599c5e547f</t>
+          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>El Car Wash</t>
+          <t>Akumin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Doral, FL, US USA</t>
+          <t>Owosso, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball</t>
+          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2854d60d8b9f2853</t>
+          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pinehurst, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Daytona Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Ashland, NE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Crown Point, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hazleton, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Florence, AL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b012c06dfa5e0cae</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Sr. DevOps Engineer - Digital Assets</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Marathon Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,77 +1921,77 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Application Architect - Test Data Management</t>
+          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
+          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Greenfield Full Stack Developer</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c851b36997bd8584</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
@@ -3553,20 +3553,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Data Engineer - API / Microservices</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior UX Software Engineer 7.26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer II</t>
+          <t>UX Software Engineer 6.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
+          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MMOTA Automation &amp; Analytics Engineer</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f370160e1fb6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Travel + Leisure Co.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer 7.26</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UX Software Engineer 6.2026</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be7881568795588b</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer - Full Stack</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33a8b4b4f37df9a</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II - Encore Program</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4065,216 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Owosso, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12ca711587212e11</t>
+          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
         </is>
       </c>
     </row>
@@ -1033,20 +1033,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d050e61b349b91</t>
+          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pinehurst, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6319ba31cc07061f</t>
+          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist (ITS)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77e9a5ce95c56bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Daytona Beach, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a93f66d14f89beb</t>
+          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061674d48a1eefb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ashland, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31eb096c82914b29</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb374443c0f901f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crown Point, IN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68ae7ec766fbf140</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,522 +1336,522 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b0bb70235da5a47</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hazleton, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0220b66ac51d5270</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b17e7aa08bf0b3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Akumin</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Florence, AL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, BigQuery, Hadoop, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=717ebd9b68e70cff</t>
+          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, Databricks, Spark, PySpark, Kafka, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=486a846548c8944d</t>
+          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d34de94764adcf6e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8062146e14fcc8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d96ea8e9dc36fab</t>
+          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Scientist (ITS)</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea9a719ad357a71</t>
+          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c2d52cb360b4df</t>
+          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer - Digital Assets</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0528faeb6919f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,94 +1861,94 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Marathon Health</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SNS, API Gateway, ECS, RDS, Azure, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620b819414083bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Warehouse Architect</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
+          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, AI</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Constellation Energy</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Databricks Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
+          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
+          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
         </is>
       </c>
     </row>
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
+          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Application Architect - Test Data Management</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,29 +2796,29 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
+          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,1230 +2841,495 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Consultant, Mobile App Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Travel + Leisure Co.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Application Architect - Test Data Management</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Early Warning Services</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76369b84a3e2fbc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Full Stack Senior Software Engineer– Investment Risk Technology</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>T. Rowe Price</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, Scala, Snowflake, PostgreSQL, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2371f7d678098e5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer - API / Microservices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>McLane Company</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer II</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Illumio</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Travel + Leisure Co.</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior UX Software Engineer 7.26</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f861df8f0188deee</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>UX Software Engineer 6.2026</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>GRVTY</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2c8b4ddce2746f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>

--- a/results/job_matches_2026-07-18.xlsx
+++ b/results/job_matches_2026-07-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer III - Python, Databricks</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Medallion Architecture, Scala, MongoDB, NoSQL, Star Schema, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=897b25c8ee04bb95</t>
+          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>onXmaps</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3992a4ede9127d14</t>
+          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, GCP, BigQuery, Scala</t>
+          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6e357f2771355c</t>
+          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Sr. Software Engineer II - Global Servicing Technology</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>onXmaps</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bozeman, MT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29b361d2f6dec61</t>
+          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quality Assurance Architect - Hadoop / Big Data / Python</t>
+          <t>Senior Platform Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40430f432f2963a7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer II - Global Servicing Technology</t>
+          <t>Integration Services Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Toll Brothers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Washington, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2799dc6e072791b7</t>
+          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Software Engineer</t>
+          <t>Sr. Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>COLLETTE TRAVEL SERVICE INC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb99900659461c29</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Integration Services Engineer</t>
+          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Toll Brothers</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Fort Washington, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, ETL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163762cb42bc6d83</t>
+          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Software Engineer, AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Constellation Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,29 +1431,29 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65fae4e16438f4c</t>
+          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Sr Data Engineer - API / Microservices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,1860 +1476,460 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3641db5c989e42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbff08fed60018ea</t>
+          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fba274cb5136e65</t>
+          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Senior AI Engineer – Apply For CircleCard</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf57f598f9ea7423</t>
+          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c96a903a5487c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca217f385c40b797</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f16272bedb7606a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86c97ae16fb951f4</t>
+          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II - Encore Program</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1ed34d678e13777</t>
+          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1676f8c172d66f91</t>
+          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54040855b7650ac2</t>
+          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f27858614b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd3bfec25e76a502</t>
+          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Databricks Data Architect</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79b417ce1eb08163</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5bdeea52df6e9ba8</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f422a8b80a284d47</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6098fb5d33d5791</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edaa8ea774783d39</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a791e0784bb1333</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f11b57c1855a365</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db1ac67fa5959580</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3730115583549ffb</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7994302f2196481d</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2fbf8d362e5c3c20</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2430f2e385edbe08</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54c29b1afc2b6ebe</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=990f6cc0f56df974</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=554ecdd2fa876e22</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4855bcc2cd682464</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49fbb2bff93a4f21</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9fb94e3ff6a4f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6725ee8dab2d001</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b80e8d6c4de7c94b</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bafebea4648af5d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Databricks Data Architect</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Concentrix</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4ce8b9543319149</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Sr. Data Warehouse Architect</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>COLLETTE TRAVEL SERVICE INC</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Pawtucket, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab0dc1d3377ff12</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect - Azure Cloud Platform &amp; Infrastructure</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, ELT, MLflow, Terraform</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3578fc92cb1c9a9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer, AI</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Constellation Energy</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, NoSQL, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af68bea7b4753eb9</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Application Architect - Test Data Management</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, Data Modeling, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e69eb5b3992ac74</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer - API / Microservices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>McLane Company</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, BigQuery, Scala, Oracle, PostgreSQL, ETL, ELT, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb03759ca911a7c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Senior Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=db2f326c8638e9dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer II</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Illumio</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da83fdc5e998cf41</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Consultant, Mobile App Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Travel + Leisure Co.</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06ab8da47aa242b</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer – Apply For CircleCard</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1593657cd51d3c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9578c5ee6ff86e13</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad76db08f630b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d43ce86d90bed8</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=06f4175ce14c5277</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II - Encore Program</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=477ade6f9df74158</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48d45f63d627c354</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08e63d65ec993a4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9ac57f31d83fabb</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7770acdfe63142da</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35403b174dad896e</t>
         </is>
